--- a/InputData/elec/RQSD/RPS Qualifying Source Definitions.xlsx
+++ b/InputData/elec/RQSD/RPS Qualifying Source Definitions.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Dropbox\NEXT Group\90. 개인 폴더\이지우\단기대응\202501 EPS 수요전망\V3\RQSD\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mary Francis Swint\Vensim\eps-southkorea\InputData\elec\RQSD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{999B5D98-C504-483A-80E8-B0F04A518698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81C95B7B-0DEC-4C7C-ABE1-F4F39296F9F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2268" yWindow="2268" windowWidth="17280" windowHeight="8880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="RQSD-BRQSD" sheetId="2" r:id="rId2"/>
+    <sheet name="RQSD-CQSD" sheetId="4" r:id="rId2"/>
     <sheet name="RQSD-RQSD" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -149,11 +149,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -161,7 +161,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -169,20 +169,20 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -190,7 +190,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -198,7 +198,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -243,8 +243,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="1" builtinId="8"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -260,9 +260,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -300,9 +300,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -335,26 +335,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -387,26 +370,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -581,22 +547,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="84.59765625" customWidth="1"/>
+    <col min="2" max="2" width="84.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -604,32 +570,32 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:2">
       <c r="B5" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:2">
       <c r="B6" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:2">
       <c r="B7" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:2">
       <c r="A10" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:2">
       <c r="A11" t="s">
         <v>24</v>
       </c>
@@ -642,18 +608,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3459CDA-62B1-42F3-87C3-37623F99200E}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE25"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="31.09765625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.8984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.453125" customWidth="1"/>
+    <col min="2" max="2" width="28.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:31">
       <c r="A1" s="2" t="s">
         <v>19</v>
       </c>
@@ -748,7 +714,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:31">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -843,7 +809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:31">
       <c r="A3" t="s">
         <v>26</v>
       </c>
@@ -938,7 +904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:31">
       <c r="A4" t="s">
         <v>27</v>
       </c>
@@ -1033,102 +999,102 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:31">
       <c r="A5" t="s">
         <v>1</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:31">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -1223,7 +1189,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:31">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -1318,7 +1284,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:31">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1413,7 +1379,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:31">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -1508,7 +1474,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:31">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -1603,7 +1569,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:31">
       <c r="A11" t="s">
         <v>6</v>
       </c>
@@ -1698,7 +1664,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:31">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -1793,7 +1759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:31">
       <c r="A13" t="s">
         <v>8</v>
       </c>
@@ -1888,16 +1854,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:31">
       <c r="A14" t="s">
         <v>12</v>
       </c>
       <c r="B14">
-        <f>B3</f>
+        <f>B2</f>
         <v>0</v>
       </c>
       <c r="C14">
-        <f t="shared" ref="C14:AE14" si="0">C3</f>
+        <f t="shared" ref="C14:AE14" si="0">C2</f>
         <v>0</v>
       </c>
       <c r="D14">
@@ -2013,7 +1979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:31">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -2108,7 +2074,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:31">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -2203,7 +2169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:31">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -2298,7 +2264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:31">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -2393,825 +2359,673 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:31">
       <c r="A19" t="s">
         <v>28</v>
       </c>
       <c r="B19">
-        <f>B2</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C19">
-        <f t="shared" ref="C19:AE19" si="1">C2</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N19">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O19">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P19">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q19">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S19">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T19">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U19">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W19">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X19">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y19">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z19">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA19">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB19">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC19">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD19">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE19">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:31">
       <c r="A20" t="s">
         <v>29</v>
       </c>
       <c r="B20">
-        <f>B4</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20">
-        <f t="shared" ref="C20:AE20" si="2">C4</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N20">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O20">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P20">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q20">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S20">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T20">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U20">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V20">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W20">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X20">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y20">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z20">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA20">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB20">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC20">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD20">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE20">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:31">
       <c r="A21" t="s">
         <v>30</v>
       </c>
       <c r="B21">
-        <f>B10</f>
         <v>1</v>
       </c>
       <c r="C21">
-        <f t="shared" ref="C21:AE21" si="3">C10</f>
         <v>1</v>
       </c>
       <c r="D21">
-        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="E21">
-        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="F21">
-        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="G21">
-        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="H21">
-        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="I21">
-        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="J21">
-        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="K21">
-        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="L21">
-        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="M21">
-        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="N21">
-        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="O21">
-        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="P21">
-        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="Q21">
-        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="R21">
-        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="S21">
-        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="T21">
-        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="U21">
-        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="V21">
-        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="W21">
-        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="X21">
-        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="Y21">
-        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="Z21">
-        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="AA21">
-        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="AB21">
-        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="AC21">
-        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="AD21">
-        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="AE21">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:31">
       <c r="A22" t="s">
         <v>31</v>
       </c>
       <c r="B22">
-        <f>B14</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C22">
-        <f t="shared" ref="C22:AE22" si="4">C14</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D22">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N22">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O22">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P22">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q22">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S22">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T22">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U22">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V22">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W22">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X22">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y22">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z22">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA22">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB22">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC22">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD22">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE22">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:31">
       <c r="A23" t="s">
         <v>32</v>
       </c>
       <c r="B23">
-        <f>B5</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C23">
-        <f t="shared" ref="C23:AE23" si="5">C5</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D23">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N23">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O23">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P23">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q23">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S23">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T23">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U23">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V23">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W23">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X23">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y23">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z23">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA23">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB23">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC23">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD23">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE23">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:31">
       <c r="A24" s="5" t="s">
         <v>33</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:31">
       <c r="A25" s="5" t="s">
         <v>34</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3221,13 +3035,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE25"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="24.59765625" customWidth="1"/>
-    <col min="2" max="2" width="22.796875" customWidth="1"/>
+    <col min="1" max="1" width="24.6328125" customWidth="1"/>
+    <col min="2" max="2" width="22.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:31">
       <c r="A1" s="2" t="s">
         <v>19</v>
       </c>
@@ -3322,7 +3136,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:31">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -3417,7 +3231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:31">
       <c r="A3" t="s">
         <v>26</v>
       </c>
@@ -3512,7 +3326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:31">
       <c r="A4" t="s">
         <v>27</v>
       </c>
@@ -3607,7 +3421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:31">
       <c r="A5" t="s">
         <v>1</v>
       </c>
@@ -3702,7 +3516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:31">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -3797,7 +3611,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:31">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -3892,7 +3706,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:31">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -3987,7 +3801,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:31">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -4082,7 +3896,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:31">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -4177,7 +3991,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:31">
       <c r="A11" t="s">
         <v>6</v>
       </c>
@@ -4272,7 +4086,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:31">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -4367,7 +4181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:31">
       <c r="A13" t="s">
         <v>8</v>
       </c>
@@ -4462,7 +4276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:31">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -4587,7 +4401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:31">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -4682,7 +4496,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:31">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -4777,7 +4591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:31">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -4872,7 +4686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:31">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -4967,7 +4781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:31">
       <c r="A19" t="s">
         <v>28</v>
       </c>
@@ -5092,7 +4906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:31">
       <c r="A20" t="s">
         <v>29</v>
       </c>
@@ -5217,7 +5031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:31">
       <c r="A21" t="s">
         <v>30</v>
       </c>
@@ -5342,7 +5156,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:31">
       <c r="A22" t="s">
         <v>31</v>
       </c>
@@ -5467,7 +5281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:31">
       <c r="A23" t="s">
         <v>32</v>
       </c>
@@ -5592,7 +5406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:31">
       <c r="A24" s="5" t="s">
         <v>33</v>
       </c>
@@ -5687,7 +5501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:31">
       <c r="A25" s="5" t="s">
         <v>34</v>
       </c>
@@ -5789,6 +5603,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E59C87379D9A4242BB3A95F198D6F941" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07a235b40ffe2d9a960bde50f6511605">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40f4d404-d193-41dc-bb72-733c1e774208" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="485fc8e6f691b86ce0aee9b7e82feca0" ns2:_="">
     <xsd:import namespace="40f4d404-d193-41dc-bb72-733c1e774208"/>
@@ -5932,29 +5761,37 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15159AFF-F622-4FDB-A8C0-FE0879517BE8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E766911-8F14-4095-89B3-4AB4ED75C0AF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B42FFB79-72A1-4B6E-9F6E-4F43C17FDE25}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B42FFB79-72A1-4B6E-9F6E-4F43C17FDE25}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E766911-8F14-4095-89B3-4AB4ED75C0AF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15159AFF-F622-4FDB-A8C0-FE0879517BE8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="40f4d404-d193-41dc-bb72-733c1e774208"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/InputData/elec/RQSD/RPS Qualifying Source Definitions.xlsx
+++ b/InputData/elec/RQSD/RPS Qualifying Source Definitions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mary Francis Swint\Vensim\eps-southkorea\InputData\elec\RQSD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81C95B7B-0DEC-4C7C-ABE1-F4F39296F9F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{844D98A9-B9C1-4F10-AAFF-09198451C1E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -3901,94 +3901,94 @@
         <v>5</v>
       </c>
       <c r="B10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:31">
@@ -5037,123 +5037,123 @@
       </c>
       <c r="B21">
         <f>B10</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C21">
         <f t="shared" ref="C21:AE21" si="3">C10</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F21">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H21">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I21">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N21">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O21">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P21">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q21">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T21">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U21">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V21">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W21">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X21">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y21">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z21">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA21">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB21">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC21">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD21">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE21">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:31">
@@ -5411,94 +5411,94 @@
         <v>33</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:31">
@@ -5506,94 +5506,94 @@
         <v>34</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -5603,21 +5603,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E59C87379D9A4242BB3A95F198D6F941" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07a235b40ffe2d9a960bde50f6511605">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40f4d404-d193-41dc-bb72-733c1e774208" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="485fc8e6f691b86ce0aee9b7e82feca0" ns2:_="">
     <xsd:import namespace="40f4d404-d193-41dc-bb72-733c1e774208"/>
@@ -5761,24 +5746,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E766911-8F14-4095-89B3-4AB4ED75C0AF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B42FFB79-72A1-4B6E-9F6E-4F43C17FDE25}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15159AFF-F622-4FDB-A8C0-FE0879517BE8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5794,4 +5777,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B42FFB79-72A1-4B6E-9F6E-4F43C17FDE25}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E766911-8F14-4095-89B3-4AB4ED75C0AF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/InputData/elec/RQSD/RPS Qualifying Source Definitions.xlsx
+++ b/InputData/elec/RQSD/RPS Qualifying Source Definitions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mary Francis Swint\Vensim\eps-southkorea\InputData\elec\RQSD\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RobbieOrvis\Models\South Korea\Models\eps-southkorea\InputData\elec\RQSD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{844D98A9-B9C1-4F10-AAFF-09198451C1E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B3B4D80-4B92-4E42-AE1F-F9D3FAD9590F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="10008" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="36">
   <si>
     <t>Source:</t>
   </si>
@@ -143,6 +143,9 @@
   </si>
   <si>
     <t>hydrogen combined cycle</t>
+  </si>
+  <si>
+    <t>2026-09-08 partner round 1: biomass set to qualify for the RPS (was 0). Korea issues RECs for bioenergy (wood pellets/chips 0.5, unused forest biomass 1.5-2.0, other bio 1.0; RPS 관리운영지침 별표2). Municipal solid waste left at 0 (only the biogenic fraction earns 0.25 and EPS MSW is 0.3 GW). Fuel cells (weight 1.9) are not an EPS source.</t>
   </si>
 </sst>
 </file>
@@ -546,10 +549,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="84.6328125" customWidth="1"/>
+    <col min="2" max="2" width="84.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -598,6 +601,11 @@
     <row r="11" spans="1:2">
       <c r="A11" t="s">
         <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -613,10 +621,10 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE25"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="25.453125" customWidth="1"/>
-    <col min="2" max="2" width="28.453125" customWidth="1"/>
+    <col min="1" max="1" width="25.44140625" customWidth="1"/>
+    <col min="2" max="2" width="28.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:31">
@@ -3035,10 +3043,10 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE25"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="24.6328125" customWidth="1"/>
-    <col min="2" max="2" width="22.81640625" customWidth="1"/>
+    <col min="1" max="1" width="24.6640625" customWidth="1"/>
+    <col min="2" max="2" width="22.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:31">
@@ -3901,94 +3909,94 @@
         <v>5</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:31">
@@ -5037,123 +5045,123 @@
       </c>
       <c r="B21">
         <f>B10</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C21">
         <f t="shared" ref="C21:AE21" si="3">C10</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E21">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N21">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O21">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P21">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q21">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T21">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U21">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W21">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X21">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y21">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z21">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA21">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB21">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC21">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD21">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE21">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:31">
@@ -5603,6 +5611,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E59C87379D9A4242BB3A95F198D6F941" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07a235b40ffe2d9a960bde50f6511605">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40f4d404-d193-41dc-bb72-733c1e774208" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="485fc8e6f691b86ce0aee9b7e82feca0" ns2:_="">
     <xsd:import namespace="40f4d404-d193-41dc-bb72-733c1e774208"/>
@@ -5746,22 +5769,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E766911-8F14-4095-89B3-4AB4ED75C0AF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B42FFB79-72A1-4B6E-9F6E-4F43C17FDE25}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15159AFF-F622-4FDB-A8C0-FE0879517BE8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5777,21 +5802,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B42FFB79-72A1-4B6E-9F6E-4F43C17FDE25}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E766911-8F14-4095-89B3-4AB4ED75C0AF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>